--- a/plan/Nodejs_Skillup_Plan_v2_revised_0731.xlsx
+++ b/plan/Nodejs_Skillup_Plan_v2_revised_0731.xlsx
@@ -523,16 +523,16 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="16"/>
+    <col customWidth="1" max="2" min="2" width="22"/>
+    <col customWidth="1" max="3" min="3" width="22"/>
+    <col customWidth="1" max="4" min="4" width="42"/>
+    <col customWidth="1" max="5" min="5" width="22"/>
+    <col customWidth="1" max="6" min="6" width="34"/>
+    <col customWidth="1" max="7" min="7" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row customHeight="1" ht="26" r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Node.js Skillup 学习规划 —— 7/31 收口修订版</t>
@@ -559,7 +559,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>原 8 周 → 应公司要求以 7/31（周五）为 end date；已完成 W1–W2，剩余收口为 4 周（W3–W6）</t>
+          <t>原 8 周调整为 7/31（周五）结束；已完成 W1-W2，剩余收口为 4 周（W3-W6）</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>最终复盘中点明整个 skillup 如何借助并驾驭 AI 即可满足公司对 AI 能力的期待</t>
+          <t>最终复盘用仓库证据说明整个 skillup 如何借助并驾驭 AI，形成可复查的 AI 协作能力证据</t>
         </is>
       </c>
     </row>
@@ -915,6 +915,6 @@
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="A14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>